--- a/skill.xlsx
+++ b/skill.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26920" windowHeight="11540"/>
+    <workbookView windowWidth="26920" windowHeight="11540" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="skill" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,6 +27,473 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="154">
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>rank</t>
+  </si>
+  <si>
+    <t>rankLevel</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>obtainMethod</t>
+  </si>
+  <si>
+    <t>attributes</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>skill_1</t>
+  </si>
+  <si>
+    <t>引气诀</t>
+  </si>
+  <si>
+    <t>凡阶</t>
+  </si>
+  <si>
+    <t>凡人入门，滋养肉身提health</t>
+  </si>
+  <si>
+    <t>商店，任务</t>
+  </si>
+  <si>
+    <t>{"health": 5}</t>
+  </si>
+  <si>
+    <t>根骨</t>
+  </si>
+  <si>
+    <t>constitution</t>
+  </si>
+  <si>
+    <t>health</t>
+  </si>
+  <si>
+    <t>skill_2</t>
+  </si>
+  <si>
+    <t>御风术</t>
+  </si>
+  <si>
+    <t>借风提速，适合短途赶路</t>
+  </si>
+  <si>
+    <t>{"speed": 2}</t>
+  </si>
+  <si>
+    <t>身法</t>
+  </si>
+  <si>
+    <t>agility</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>skill_3</t>
+  </si>
+  <si>
+    <t>静心诀</t>
+  </si>
+  <si>
+    <t>静心聚灵，避免走火入魔</t>
+  </si>
+  <si>
+    <t>{"mana": 5}</t>
+  </si>
+  <si>
+    <t>机缘</t>
+  </si>
+  <si>
+    <t>luck</t>
+  </si>
+  <si>
+    <t>灵力</t>
+  </si>
+  <si>
+    <t>mana</t>
+  </si>
+  <si>
+    <t>skill_4</t>
+  </si>
+  <si>
+    <t>纳运诀</t>
+  </si>
+  <si>
+    <t>粗浅聚运，提升暴击概率</t>
+  </si>
+  <si>
+    <t>{"criticalRate": 0.005}</t>
+  </si>
+  <si>
+    <t>悟性</t>
+  </si>
+  <si>
+    <t>wisdom</t>
+  </si>
+  <si>
+    <t>暴击</t>
+  </si>
+  <si>
+    <t>criticalRate</t>
+  </si>
+  <si>
+    <t>skill_5</t>
+  </si>
+  <si>
+    <t>灵葫锻体诀</t>
+  </si>
+  <si>
+    <t>灵阶</t>
+  </si>
+  <si>
+    <t>灵葫炼体，增幅health</t>
+  </si>
+  <si>
+    <t>{"health": 8}</t>
+  </si>
+  <si>
+    <t>skill_6</t>
+  </si>
+  <si>
+    <t>飞虹遁术</t>
+  </si>
+  <si>
+    <t>化虹而行，速度远超御风</t>
+  </si>
+  <si>
+    <t>{"speed": 3}</t>
+  </si>
+  <si>
+    <t>迅捷</t>
+  </si>
+  <si>
+    <t>skill_7</t>
+  </si>
+  <si>
+    <t>清心灵诀</t>
+  </si>
+  <si>
+    <t>净化杂念，提升灵力纯度</t>
+  </si>
+  <si>
+    <t>{"mana": 8}</t>
+  </si>
+  <si>
+    <t>神识</t>
+  </si>
+  <si>
+    <t>spirit</t>
+  </si>
+  <si>
+    <t>skill_8</t>
+  </si>
+  <si>
+    <t>鸿运诀</t>
+  </si>
+  <si>
+    <t>引先天气运，增暴击</t>
+  </si>
+  <si>
+    <t>{"criticalRate": 0.008}</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
+    <t>attack</t>
+  </si>
+  <si>
+    <t>skill_9</t>
+  </si>
+  <si>
+    <t>玄黄炼体诀</t>
+  </si>
+  <si>
+    <t>黄阶</t>
+  </si>
+  <si>
+    <t>玄黄淬体，神魔立身之本</t>
+  </si>
+  <si>
+    <t>{"health": 12}</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>defense</t>
+  </si>
+  <si>
+    <t>skill_10</t>
+  </si>
+  <si>
+    <t>裂空遁法</t>
+  </si>
+  <si>
+    <t>裂空瞬移，快如惊雷</t>
+  </si>
+  <si>
+    <t>{"speed": 5}</t>
+  </si>
+  <si>
+    <t>skill_11</t>
+  </si>
+  <si>
+    <t>玄慧心经</t>
+  </si>
+  <si>
+    <t>提升灵力，助力突破瓶颈</t>
+  </si>
+  <si>
+    <t>{"mana": 12}</t>
+  </si>
+  <si>
+    <t>闪避</t>
+  </si>
+  <si>
+    <t>dodge</t>
+  </si>
+  <si>
+    <t>skill_12</t>
+  </si>
+  <si>
+    <t>玄运天诀</t>
+  </si>
+  <si>
+    <t>聚玄运气韵，避凶险</t>
+  </si>
+  <si>
+    <t>{"criticalRate": 0.01}</t>
+  </si>
+  <si>
+    <t>skill_13</t>
+  </si>
+  <si>
+    <t>地魁金身诀</t>
+  </si>
+  <si>
+    <t>玄阶</t>
+  </si>
+  <si>
+    <t>凝大地金身，硬抗准圣</t>
+  </si>
+  <si>
+    <t>商店，任务，宗门</t>
+  </si>
+  <si>
+    <t>{"health": 18}</t>
+  </si>
+  <si>
+    <t>skill_14</t>
+  </si>
+  <si>
+    <t>无影遁</t>
+  </si>
+  <si>
+    <t>无影无踪，准圣难寻</t>
+  </si>
+  <si>
+    <t>{"speed": 7}</t>
+  </si>
+  <si>
+    <t>skill_15</t>
+  </si>
+  <si>
+    <t>地心灵慧经</t>
+  </si>
+  <si>
+    <t>滋养神识，助破准圣</t>
+  </si>
+  <si>
+    <t>{"mana": 18}</t>
+  </si>
+  <si>
+    <t>skill_16</t>
+  </si>
+  <si>
+    <t>地煞鸿运经</t>
+  </si>
+  <si>
+    <t>引地煞气运，牵天地机缘</t>
+  </si>
+  <si>
+    <t>{"criticalRate": 0.015}</t>
+  </si>
+  <si>
+    <t>skill_17</t>
+  </si>
+  <si>
+    <t>大品天仙诀·根骨篇</t>
+  </si>
+  <si>
+    <t>地阶</t>
+  </si>
+  <si>
+    <t>道门正统，淬炼先天根骨</t>
+  </si>
+  <si>
+    <t>{"constitution": 2}</t>
+  </si>
+  <si>
+    <t>skill_18</t>
+  </si>
+  <si>
+    <t>天罡遁法·迅捷篇</t>
+  </si>
+  <si>
+    <t>天罡淬身，提升迅捷</t>
+  </si>
+  <si>
+    <t>{"agility": 2}</t>
+  </si>
+  <si>
+    <t>skill_19</t>
+  </si>
+  <si>
+    <t>玉清仙法·悟性篇</t>
+  </si>
+  <si>
+    <t>玉清传承，提升悟性</t>
+  </si>
+  <si>
+    <t>{"wisdom": 2}</t>
+  </si>
+  <si>
+    <t>skill_20</t>
+  </si>
+  <si>
+    <t>天命大运诀·机缘篇</t>
+  </si>
+  <si>
+    <t>提升机缘，易获至宝</t>
+  </si>
+  <si>
+    <t>{"luck": 2}</t>
+  </si>
+  <si>
+    <t>skill_21</t>
+  </si>
+  <si>
+    <t>九转玄功·根骨经</t>
+  </si>
+  <si>
+    <t>天阶</t>
+  </si>
+  <si>
+    <t>九转淬骨，肉身成圣法门</t>
+  </si>
+  <si>
+    <t>{"constitution": 3}</t>
+  </si>
+  <si>
+    <t>skill_22</t>
+  </si>
+  <si>
+    <t>混沌极速法·迅捷经</t>
+  </si>
+  <si>
+    <t>混沌法则，速度破空间</t>
+  </si>
+  <si>
+    <t>{"agility": 3}</t>
+  </si>
+  <si>
+    <t>skill_23</t>
+  </si>
+  <si>
+    <t>九转元功·悟性经</t>
+  </si>
+  <si>
+    <t>九转悟道，速领大道</t>
+  </si>
+  <si>
+    <t>{"wisdom": 3}</t>
+  </si>
+  <si>
+    <t>skill_24</t>
+  </si>
+  <si>
+    <t>混元道经·机缘经</t>
+  </si>
+  <si>
+    <t>混元气运，引本源机缘</t>
+  </si>
+  <si>
+    <t>{"luck": 3}</t>
+  </si>
+  <si>
+    <t>skill_25</t>
+  </si>
+  <si>
+    <t>盘古真身诀·根骨天书</t>
+  </si>
+  <si>
+    <t>圣阶</t>
+  </si>
+  <si>
+    <t>盘古传承，根骨冠洪荒</t>
+  </si>
+  <si>
+    <t>活动</t>
+  </si>
+  <si>
+    <t>{"constitution": 5}</t>
+  </si>
+  <si>
+    <t>skill_26</t>
+  </si>
+  <si>
+    <t>鲲鹏北冥遁·迅捷天书</t>
+  </si>
+  <si>
+    <t>鲲鹏传承，可混沌穿梭</t>
+  </si>
+  <si>
+    <t>{"agility": 5}</t>
+  </si>
+  <si>
+    <t>skill_27</t>
+  </si>
+  <si>
+    <t>鸿蒙大道诀·悟性天书</t>
+  </si>
+  <si>
+    <t>鸿蒙本源，悟性达混沌</t>
+  </si>
+  <si>
+    <t>{"wisdom": 5}</t>
+  </si>
+  <si>
+    <t>skill_28</t>
+  </si>
+  <si>
+    <t>混沌本源诀·机缘天书</t>
+  </si>
+  <si>
+    <t>混沌气运，引至宝机缘</t>
+  </si>
+  <si>
+    <t>{"luck": 5}</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
@@ -34,9 +502,16 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -381,12 +856,53 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -507,139 +1023,154 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -693,7 +1224,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -887,25 +1425,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1166,6 +1704,1041 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:T30"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="4" max="4" width="10.3846153846154" customWidth="1"/>
+    <col min="5" max="5" width="23.8461538461538" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="22.5384615384615" customWidth="1"/>
+    <col min="10" max="10" width="8.97115384615385" customWidth="1"/>
+    <col min="11" max="11" width="6.30769230769231" customWidth="1"/>
+    <col min="12" max="12" width="12.5384615384615" customWidth="1"/>
+    <col min="14" max="14" width="4.61538461538461" customWidth="1"/>
+    <col min="15" max="15" width="12.5384615384615" customWidth="1"/>
+    <col min="19" max="19" width="8.97115384615385" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.55" spans="1:20">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="31.75" spans="1:20">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" t="str">
+        <f>A2&amp;$H$1&amp;B2&amp;$H$1&amp;C2&amp;$H$1&amp;D2&amp;$H$1&amp;E2&amp;$H$1&amp;F2&amp;$H$1&amp;G2</f>
+        <v>skill_1,引气诀,凡阶,1,凡人入门，滋养肉身提health,商店，任务,{"health": 5}</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2"/>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="17.55" spans="1:20">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="str">
+        <f t="shared" ref="H3:H29" si="0">A3&amp;$H$1&amp;B3&amp;$H$1&amp;C3&amp;$H$1&amp;D3&amp;$H$1&amp;E3&amp;$H$1&amp;F3&amp;$H$1&amp;G3</f>
+        <v>skill_2,御风术,凡阶,1,借风提速，适合短途赶路,商店，任务,{"speed": 2}</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3"/>
+      <c r="N3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" ht="17.55" spans="1:20">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_3,静心诀,凡阶,1,静心聚灵，避免走火入魔,商店，任务,{"mana": 5}</v>
+      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4"/>
+      <c r="N4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" t="s">
+        <v>30</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="T4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="17.55" spans="1:20">
+      <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_4,纳运诀,凡阶,1,粗浅聚运，提升暴击概率,商店，任务,{"criticalRate": 0.005}</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="3"/>
+      <c r="L5"/>
+      <c r="N5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="31.75" spans="1:20">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_5,灵葫锻体诀,灵阶,2,灵葫炼体，增幅health,商店，任务,{"health": 8}</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6"/>
+      <c r="N6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="O6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" ht="17.55" spans="1:20">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_6,飞虹遁术,灵阶,2,化虹而行，速度远超御风,商店，任务,{"speed": 3}</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7"/>
+      <c r="N7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O7" t="s">
+        <v>32</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" ht="17.55" spans="1:20">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_7,清心灵诀,灵阶,2,净化杂念，提升灵力纯度,商店，任务,{"mana": 8}</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8"/>
+      <c r="N8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" t="s">
+        <v>56</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" ht="17.55" spans="1:20">
+      <c r="A9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_8,鸿运诀,灵阶,2,引先天气运，增暴击,商店，任务,{"criticalRate": 0.008}</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="3"/>
+      <c r="L9"/>
+      <c r="N9" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O9" t="s">
+        <v>62</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="17.55" spans="1:20">
+      <c r="A10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_9,玄黄炼体诀,黄阶,3,玄黄淬体，神魔立身之本,商店，任务,{"health": 12}</v>
+      </c>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10"/>
+      <c r="N10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="O10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" ht="17.55" spans="1:20">
+      <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_10,裂空遁法,黄阶,3,裂空瞬移，快如惊雷,商店，任务,{"speed": 5}</v>
+      </c>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11"/>
+      <c r="N11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="17.55" spans="1:20">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_11,玄慧心经,黄阶,3,提升灵力，助力突破瓶颈,商店，任务,{"mana": 12}</v>
+      </c>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12"/>
+      <c r="N12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" ht="17.55" spans="1:20">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_12,玄运天诀,黄阶,3,聚玄运气韵，避凶险,商店，任务,{"criticalRate": 0.01}</v>
+      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="3"/>
+      <c r="L13"/>
+      <c r="N13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="17.55" spans="1:20">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_13,地魁金身诀,玄阶,4,凝大地金身，硬抗准圣,商店，任务，宗门,{"health": 18}</v>
+      </c>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14"/>
+      <c r="N14" s="1"/>
+    </row>
+    <row r="15" ht="17.55" spans="1:20">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" t="s">
+        <v>93</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_14,无影遁,玄阶,4,无影无踪，准圣难寻,商店，任务，宗门,{"speed": 7}</v>
+      </c>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15"/>
+      <c r="N15" s="1"/>
+    </row>
+    <row r="16" ht="17.55" spans="1:20">
+      <c r="A16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_15,地心灵慧经,玄阶,4,滋养神识，助破准圣,商店，任务，宗门,{"mana": 18}</v>
+      </c>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" ht="17.55" spans="1:14">
+      <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" t="s">
+        <v>86</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F17" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_16,地煞鸿运经,玄阶,4,引地煞气运，牵天地机缘,商店，任务，宗门,{"criticalRate": 0.015}</v>
+      </c>
+      <c r="J17" s="1"/>
+      <c r="K17" s="3"/>
+      <c r="L17"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" ht="17.55" spans="1:14">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>88</v>
+      </c>
+      <c r="G18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_17,大品天仙诀·根骨篇,地阶,5,道门正统，淬炼先天根骨,商店，任务，宗门,{"constitution": 2}</v>
+      </c>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" ht="17.55" spans="1:14">
+      <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19">
+        <v>5</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F19" t="s">
+        <v>88</v>
+      </c>
+      <c r="G19" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_18,天罡遁法·迅捷篇,地阶,5,天罡淬身，提升迅捷,商店，任务，宗门,{"agility": 2}</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" ht="17.55" spans="1:14">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="F20" t="s">
+        <v>88</v>
+      </c>
+      <c r="G20" t="s">
+        <v>114</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_19,玉清仙法·悟性篇,地阶,5,玉清传承，提升悟性,商店，任务，宗门,{"wisdom": 2}</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20"/>
+      <c r="N20" s="1"/>
+    </row>
+    <row r="21" ht="17.55" spans="1:14">
+      <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" t="s">
+        <v>104</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_20,天命大运诀·机缘篇,地阶,5,提升机缘，易获至宝,商店，任务，宗门,{"luck": 2}</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21"/>
+      <c r="N21" s="1"/>
+    </row>
+    <row r="22" ht="17.55" spans="1:14">
+      <c r="A22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" t="s">
+        <v>121</v>
+      </c>
+      <c r="D22">
+        <v>6</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F22" t="s">
+        <v>88</v>
+      </c>
+      <c r="G22" t="s">
+        <v>123</v>
+      </c>
+      <c r="H22" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_21,九转玄功·根骨经,天阶,6,九转淬骨，肉身成圣法门,商店，任务，宗门,{"constitution": 3}</v>
+      </c>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" ht="17.55" spans="1:14">
+      <c r="A23" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" t="s">
+        <v>88</v>
+      </c>
+      <c r="G23" t="s">
+        <v>127</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_22,混沌极速法·迅捷经,天阶,6,混沌法则，速度破空间,商店，任务，宗门,{"agility": 3}</v>
+      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23"/>
+      <c r="N23" s="1"/>
+    </row>
+    <row r="24" ht="17.55" spans="1:14">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F24" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" t="s">
+        <v>131</v>
+      </c>
+      <c r="H24" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_23,九转元功·悟性经,天阶,6,九转悟道，速领大道,商店，任务，宗门,{"wisdom": 3}</v>
+      </c>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24"/>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" ht="17.55" spans="1:14">
+      <c r="A25" t="s">
+        <v>132</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25">
+        <v>6</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F25" t="s">
+        <v>88</v>
+      </c>
+      <c r="G25" t="s">
+        <v>135</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_24,混元道经·机缘经,天阶,6,混元气运，引本源机缘,商店，任务，宗门,{"luck": 3}</v>
+      </c>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25"/>
+      <c r="N25" s="1"/>
+    </row>
+    <row r="26" ht="17.55" spans="1:14">
+      <c r="A26" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" t="s">
+        <v>138</v>
+      </c>
+      <c r="D26">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F26" t="s">
+        <v>140</v>
+      </c>
+      <c r="G26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_25,盘古真身诀·根骨天书,圣阶,7,盘古传承，根骨冠洪荒,活动,{"constitution": 5}</v>
+      </c>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" ht="17.55" spans="1:14">
+      <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F27" t="s">
+        <v>140</v>
+      </c>
+      <c r="G27" t="s">
+        <v>145</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_26,鲲鹏北冥遁·迅捷天书,圣阶,7,鲲鹏传承，可混沌穿梭,活动,{"agility": 5}</v>
+      </c>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27"/>
+      <c r="N27" s="1"/>
+    </row>
+    <row r="28" ht="18.3" customHeight="1" spans="1:14">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_27,鸿蒙大道诀·悟性天书,圣阶,7,鸿蒙本源，悟性达混沌,活动,{"wisdom": 5}</v>
+      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28"/>
+      <c r="N28" s="1"/>
+    </row>
+    <row r="29" ht="17.55" spans="1:14">
+      <c r="A29" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>138</v>
+      </c>
+      <c r="D29">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F29" t="s">
+        <v>140</v>
+      </c>
+      <c r="G29" t="s">
+        <v>153</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="0"/>
+        <v>skill_28,混沌本源诀·机缘天书,圣阶,7,混沌气运，引至宝机缘,活动,{"luck": 5}</v>
+      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="4"/>
+      <c r="N29" s="1"/>
+    </row>
+    <row r="30" ht="17.55" spans="1:14">
+      <c r="K30" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="K29:K30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B1:B30 B33:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <sheetData/>
